--- a/artfynd/A 11630-2025 artfynd.xlsx
+++ b/artfynd/A 11630-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121244898</v>
+        <v>121244899</v>
       </c>
       <c r="B2" t="n">
-        <v>92024</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>701710</v>
+        <v>701717</v>
       </c>
       <c r="R2" t="n">
-        <v>7239098</v>
+        <v>7239093</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121244900</v>
+        <v>121244901</v>
       </c>
       <c r="B3" t="n">
-        <v>92000</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>701704</v>
+        <v>701707</v>
       </c>
       <c r="R3" t="n">
-        <v>7239132</v>
+        <v>7239138</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,19 +877,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121244903</v>
+        <v>121244902</v>
       </c>
       <c r="B4" t="n">
-        <v>91996</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -927,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>701649</v>
+        <v>701674</v>
       </c>
       <c r="R4" t="n">
-        <v>7239169</v>
+        <v>7239139</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121244897</v>
+        <v>121244903</v>
       </c>
       <c r="B5" t="n">
-        <v>77993</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>701696</v>
+        <v>701649</v>
       </c>
       <c r="R5" t="n">
-        <v>7239117</v>
+        <v>7239169</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,19 +1079,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121244902</v>
+        <v>121244905</v>
       </c>
       <c r="B6" t="n">
-        <v>91996</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1139,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>701674</v>
+        <v>701668</v>
       </c>
       <c r="R6" t="n">
-        <v>7239139</v>
+        <v>7239180</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,37 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121244901</v>
+        <v>121244900</v>
       </c>
       <c r="B7" t="n">
-        <v>91996</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>701707</v>
+        <v>701704</v>
       </c>
       <c r="R7" t="n">
-        <v>7239138</v>
+        <v>7239132</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,37 +1281,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121244899</v>
+        <v>121244897</v>
       </c>
       <c r="B8" t="n">
-        <v>91996</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>701717</v>
+        <v>701696</v>
       </c>
       <c r="R8" t="n">
-        <v>7239093</v>
+        <v>7239117</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1410,112 +1375,6 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr">
-        <is>
-          <t>Sweco naturvärdesinventering och artinventering</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>121244905</v>
-      </c>
-      <c r="B9" t="n">
-        <v>91996</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Mörtträskheden, Pi lm</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>701668</v>
-      </c>
-      <c r="R9" t="n">
-        <v>7239180</v>
-      </c>
-      <c r="S9" t="n">
-        <v>10</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Arvidsjaur</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Arvidsjaur</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Elin Eriksson</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Elin Eriksson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
         <is>
           <t>Sweco naturvärdesinventering och artinventering</t>
         </is>

--- a/artfynd/A 11630-2025 artfynd.xlsx
+++ b/artfynd/A 11630-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Sweco naturvärdesinventering och artinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121244899</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Sweco naturvärdesinventering och artinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121244901</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Sweco naturvärdesinventering och artinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121244902</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Sweco naturvärdesinventering och artinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121244903</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Sweco naturvärdesinventering och artinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121244905</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>Sweco naturvärdesinventering och artinventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121244900</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,8 +1414,22 @@
           <t>Sweco naturvärdesinventering och artinventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121244897</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>